--- a/data/trans_orig/IP04F-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131254</t>
+          <t>131748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140629</t>
+          <t>140569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130506</t>
+          <t>130284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140263</t>
+          <t>140184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>265961</t>
+          <t>266636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278964</t>
+          <t>278852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14816</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24459</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202017</t>
+          <t>202097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216897</t>
+          <t>216279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239637</t>
+          <t>239519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254035</t>
+          <t>255060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>446885</t>
+          <t>445174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>468149</t>
+          <t>467194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31798</t>
+          <t>31718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>28038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33223</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>56198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128784</t>
+          <t>129495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142383</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130740</t>
+          <t>130462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144232</t>
+          <t>144593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263747</t>
+          <t>264352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283443</t>
+          <t>283692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26380</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>26903</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48782</t>
+          <t>48177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139640</t>
+          <t>139393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154388</t>
+          <t>154477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151221</t>
+          <t>151568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165494</t>
+          <t>165236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>295615</t>
+          <t>295076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316172</t>
+          <t>316119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30320</t>
+          <t>30567</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28104</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33113</t>
+          <t>33166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>54209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>616173</t>
+          <t>616498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>643538</t>
+          <t>642454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>669599</t>
+          <t>668705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694777</t>
+          <t>694298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1293194</t>
+          <t>1292995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1330548</t>
+          <t>1330131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>87539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>55270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79969</t>
+          <t>80863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>123474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160411</t>
+          <t>160610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116867</t>
+          <t>116226</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125694</t>
+          <t>125971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111090</t>
+          <t>111729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231191</t>
+          <t>231410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244327</t>
+          <t>243892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14212</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>23833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178562</t>
+          <t>177992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192219</t>
+          <t>192607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>231212</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>244457</t>
+          <t>244671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>414004</t>
+          <t>414301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>433795</t>
+          <t>433508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50924</t>
+          <t>50627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170395</t>
+          <t>170055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181282</t>
+          <t>181001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163463</t>
+          <t>163673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175555</t>
+          <t>175866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>337404</t>
+          <t>338264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>354074</t>
+          <t>353940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21677</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144630</t>
+          <t>145317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159163</t>
+          <t>159205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146714</t>
+          <t>146253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160354</t>
+          <t>160494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>296133</t>
+          <t>296832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316187</t>
+          <t>316436</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28147</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>28468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48771</t>
+          <t>48072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>624673</t>
+          <t>626864</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>649068</t>
+          <t>649469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>668091</t>
+          <t>668554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>692183</t>
+          <t>691154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1300595</t>
+          <t>1297779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1333907</t>
+          <t>1333413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50824</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75219</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45900</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69992</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104068</t>
+          <t>104562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137380</t>
+          <t>140196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04F-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Edad-trans_orig.xlsx
@@ -542,7 +542,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -553,7 +553,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -721,72 +721,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>136431</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>130569</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>140317</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>136782</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>131748</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>140569</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>131871</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>140600</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>94,27%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>136431</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>130284</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>140184</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266636</t>
+          <t>265061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278852</t>
+          <t>279165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -839,67 +839,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>8891</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14753</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>8316</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13350</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4498</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13227</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>5,73%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5138</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11568</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -947,57 +947,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145322</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145322</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145322</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>145098</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>145098</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>145098</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145322</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145322</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145322</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1064,72 +1064,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>247924</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>239414</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>254146</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>89,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>210144</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>202097</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>216279</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>201347</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>216481</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>89,88%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>247924</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>239519</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>255060</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>445174</t>
+          <t>446016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>467194</t>
+          <t>467125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -1177,72 +1177,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19633</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13411</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28143</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>23671</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17536</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31718</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17334</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>32468</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10,12%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19633</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12497</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>28038</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>34247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56198</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1290,57 +1290,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267557</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267557</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267557</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>233815</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>233815</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>233815</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267557</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267557</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267557</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1407,72 +1407,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>138808</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>131518</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>145126</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>88,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136270</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>129495</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>142507</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>128804</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>142049</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>87,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>138808</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>130462</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>144593</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>264352</t>
+          <t>264037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283692</t>
+          <t>283931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -1520,72 +1520,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18557</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25847</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>18894</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12657</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25669</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26360</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>12,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18557</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>12772</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26903</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48177</t>
+          <t>48492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -1633,57 +1633,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157365</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157365</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157365</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157365</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157365</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1750,72 +1750,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>159171</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>150803</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>165007</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>147712</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>139393</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>154477</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>139454</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>154154</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>86,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>159171</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>151568</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>165236</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>295076</t>
+          <t>296604</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316119</t>
+          <t>316075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -1863,72 +1863,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20154</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14318</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28522</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>22248</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15483</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30567</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15806</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30506</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>20154</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14089</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27757</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33166</t>
+          <t>33210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54209</t>
+          <t>52681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -1976,57 +1976,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179325</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179325</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179325</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169960</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169960</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169960</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179325</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179325</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2093,72 +2093,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>682333</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>668068</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>694133</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>91,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>89,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>630907</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>616498</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>642454</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>617404</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>643024</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>89,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>682333</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>668705</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>694298</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1292995</t>
+          <t>1291404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1330131</t>
+          <t>1331029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -2206,72 +2206,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>55435</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>81500</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>73130</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>61583</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>87539</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>61013</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>86633</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>67235</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>55270</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>80863</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123474</t>
+          <t>122576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160610</t>
+          <t>162201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2319,57 +2319,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704037</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704037</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704037</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2500,7 +2500,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>116743</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>110603</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>120224</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>89,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>121977</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>116226</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>125971</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>116890</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>125985</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>93,06%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>116743</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>111729</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>120261</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231410</t>
+          <t>231530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243892</t>
+          <t>243966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7421</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13561</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9102</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5108</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14853</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5094</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,94%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7421</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3903</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12435</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>23713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131079</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131079</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131079</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>238883</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>231498</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>244810</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>90,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>186003</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>177992</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>192607</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>177395</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>192548</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>89,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>85,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>238883</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>230842</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>244671</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>414301</t>
+          <t>413518</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>433508</t>
+          <t>433155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17770</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11843</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25155</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>22272</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15668</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30283</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15727</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30880</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17770</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11982</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>25811</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31420</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50627</t>
+          <t>51410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>256653</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>256653</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>256653</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208275</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208275</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208275</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>256653</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>256653</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>256653</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3354,107 +3354,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>170535</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>163113</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>175553</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>176404</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>170055</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>181001</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>169691</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>181244</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>93,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>170535</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>163673</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>175866</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>92,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>346939</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>337152</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>354203</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>94,99%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>346939</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>338264</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>353940</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -3467,107 +3467,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14605</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9587</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22027</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11357</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6760</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17706</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6517</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18070</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>6,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>14605</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9274</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21467</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>25962</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>18698</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>35749</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>25962</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>18961</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>34637</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>185140</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>185140</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>185140</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>187761</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>187761</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>187761</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>185140</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>185140</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>185140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3697,72 +3697,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>154306</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>146349</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>160277</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>89,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>85,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>153213</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>145317</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>159205</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>145249</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>158927</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>88,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>84,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>154306</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>146253</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>160494</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>296832</t>
+          <t>296117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316436</t>
+          <t>316347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -3810,72 +3810,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17821</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11850</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25778</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>19564</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13572</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27460</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13850</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27528</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>11,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>17821</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>11633</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>25874</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28468</t>
+          <t>28557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48072</t>
+          <t>48787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -3923,57 +3923,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172127</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172127</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172127</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172777</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172777</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172777</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172127</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172127</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172127</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4040,72 +4040,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>680466</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>667569</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>690857</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>959</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>637596</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>626864</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>649469</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>623377</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>647722</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>91,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>680466</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>668554</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>691154</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1297779</t>
+          <t>1298023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1333413</t>
+          <t>1334574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -4153,72 +4153,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47226</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>70514</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>62296</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>50423</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>73028</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>52170</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>76515</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>46929</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>69529</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104562</t>
+          <t>103401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140196</t>
+          <t>139952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -4266,57 +4266,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>699892</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>699892</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>699892</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
